--- a/test_doc/new_org/syllabus_science.xlsx
+++ b/test_doc/new_org/syllabus_science.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>Periods</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -447,6 +452,11 @@
       <c r="C2" t="n">
         <v>3</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -472,6 +482,11 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -507,6 +522,11 @@
       <c r="C7" t="n">
         <v>3</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -532,6 +552,11 @@
       <c r="C9" t="n">
         <v>3</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -557,6 +582,11 @@
       <c r="C11" t="n">
         <v>3</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -582,6 +612,11 @@
       <c r="C13" t="n">
         <v>3</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Term 1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -607,6 +642,11 @@
       <c r="C15" t="n">
         <v>3</v>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -642,6 +682,11 @@
       <c r="C18" t="n">
         <v>3</v>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -677,6 +722,11 @@
       <c r="C21" t="n">
         <v>4</v>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -702,6 +752,11 @@
       <c r="C23" t="n">
         <v>3</v>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -736,6 +791,11 @@
       </c>
       <c r="C26" t="n">
         <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Term 2</t>
+        </is>
       </c>
     </row>
     <row r="27">
